--- a/patient_registration_form_templates/025_mri_screening_form--patient_registration_form_templates.xlsx
+++ b/patient_registration_form_templates/025_mri_screening_form--patient_registration_form_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mri_info_form</t>
+          <t>date_of_birth_form</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MRI Information</t>
+          <t>Date of Birth</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,7 +561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -577,47 +577,47 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>emergency_contacts_form</t>
+          <t>medical_history_form</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Emergency Contacts</t>
+          <t>Medical History</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>medical_history_form</t>
+          <t>medical_conditions_form</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Medical History</t>
+          <t>Medical Conditions</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>medical_conditions_form</t>
+          <t>medication_info_form</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Medical Conditions</t>
+          <t>Medication Information</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>medication_info_form</t>
+          <t>mri_info_form</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Medication Information</t>
+          <t>MRI Information</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,40 +676,40 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>hipaa_form</t>
+          <t>emergency_contact_form</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>HIPAA</t>
+          <t>Emergency Contacts</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>signature_form</t>
+          <t>contact_info_2_form</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Signature</t>
+          <t>Contact Information 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,412 +722,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>date_of_birth_form</t>
+          <t>medical_condition_info_form</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Date of Birth</t>
+          <t>Medical Condition Info</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>emergency_contacts_1_form</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Emergency Contacts 1</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>contact_info_form</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Contact Information 1</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>medical_history_1_form</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Medical History 1</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>medical_conditions_1_form</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Medical Conditions 1</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>medical_history_2_form</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Medical History 2</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>medication_info_form</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Medication Information</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>mri_info_1_form</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>MRI Information 1</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>contact_info_1_form</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Contact Information 1</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>contact_info_2_form</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Contact Information 2</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>medical_condition_info_form</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Medical Condition Info</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>medical_condition_1_form</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Medical Conditions 1</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>mri_equipment_info_form</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>MRI Equipment Info</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>mri_equipment_form</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>MRI Equipment</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>mri_equipment_1_form</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>MRI Equipment 1</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>mri_equipment_2_form</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>MRI Equipment 2</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>signature_1_form</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Signature 1</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>signature_2_form</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Signature 2</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1144,12 +753,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1172,408 +781,306 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>emergency_contacts_1_form_choices</t>
+          <t>contact_info_form_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'john'}</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'John'}</t>
+          <t>John</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>emergency_contacts_1_form_choices</t>
+          <t>contact_info_form_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'jane'}</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Jane'}</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>emergency_contacts_1_form_choices</t>
+          <t>contact_info_form_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'bob'}</t>
+          <t>bob</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Bob'}</t>
+          <t>Bob</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>contact_info_form_choices</t>
+          <t>medical_history_form_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'john'}</t>
+          <t>heart_condition</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'John'}</t>
+          <t>Heart condition</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>contact_info_form_choices</t>
+          <t>medical_history_form_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'jane'}</t>
+          <t>asthma</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Jane'}</t>
+          <t>Asthma</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>contact_info_form_choices</t>
+          <t>medical_history_form_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'bob'}</t>
+          <t>diabetes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Bob'}</t>
+          <t>Diabetes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>medical_history_1_form_choices</t>
+          <t>medical_conditions_form_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'heart_condition'}</t>
+          <t>heart_condition</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Heart condition'}</t>
+          <t>Heart condition</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>medical_history_1_form_choices</t>
+          <t>medical_conditions_form_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'asthma'}</t>
+          <t>asthma</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Asthma'}</t>
+          <t>Asthma</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>medical_history_1_form_choices</t>
+          <t>medical_conditions_form_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'diabetes'}</t>
+          <t>diabetes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Diabetes'}</t>
+          <t>Diabetes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>medical_conditions_1_form_choices</t>
+          <t>medication_info_form_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'heart_condition'}</t>
+          <t>heart_medication</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Heart condition'}</t>
+          <t>Heart medication</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>medical_conditions_1_form_choices</t>
+          <t>medication_info_form_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'asthma'}</t>
+          <t>asthma_medication</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Asthma'}</t>
+          <t>Asthma medication</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>medical_conditions_1_form_choices</t>
+          <t>medication_info_form_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'diabetes'}</t>
+          <t>diabetes_medication</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Diabetes'}</t>
+          <t>Diabetes medication</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>medical_history_2_form_choices</t>
+          <t>emergency_contact_form_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'heart_condition'}</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Heart condition'}</t>
+          <t>John</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>medical_history_2_form_choices</t>
+          <t>emergency_contact_form_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'asthma'}</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Asthma'}</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>medical_history_2_form_choices</t>
+          <t>emergency_contact_form_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'diabetes'}</t>
+          <t>bob</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Diabetes'}</t>
+          <t>Bob</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>medication_info_form_choices</t>
+          <t>contact_info_2_form_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'heart_medication'}</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Heart medication'}</t>
+          <t>John</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>medication_info_form_choices</t>
+          <t>contact_info_2_form_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'asthma_medication'}</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Asthma medication'}</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>medication_info_form_choices</t>
+          <t>contact_info_2_form_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'diabetes_medication'}</t>
+          <t>bob</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Diabetes medication'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>contact_info_1_form_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>{'value':_'john'}</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>{'value': 'John'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>contact_info_1_form_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>{'value':_'jane'}</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>{'value': 'Jane'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>contact_info_1_form_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>{'value':_'bob'}</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>{'value': 'Bob'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>contact_info_2_form_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>{'value':_'john'}</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>{'value': 'John'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>contact_info_2_form_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>{'value':_'jane'}</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>{'value': 'Jane'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>contact_info_2_form_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>{'value':_'bob'}</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>{'value': 'Bob'}</t>
+          <t>Bob</t>
         </is>
       </c>
     </row>
